--- a/Result/profitability/3450.xlsx
+++ b/Result/profitability/3450.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.28</v>
       </c>
       <c r="M2" t="n">
-        <v>1.1275</v>
+        <v>1.25875</v>
       </c>
       <c r="N2" t="n">
-        <v>28.165</v>
+        <v>28.76625</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.44</v>
       </c>
       <c r="M3" t="n">
-        <v>1.0525</v>
+        <v>1.06375</v>
       </c>
       <c r="N3" t="n">
-        <v>28.41625</v>
+        <v>28.27125</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.47</v>
       </c>
       <c r="M4" t="n">
-        <v>0.86125</v>
+        <v>0.83</v>
       </c>
       <c r="N4" t="n">
-        <v>27.58625</v>
+        <v>27.1125</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>0.1</v>
       </c>
       <c r="M5" t="n">
-        <v>0.5812499999999999</v>
+        <v>0.7762499999999999</v>
       </c>
       <c r="N5" t="n">
-        <v>24.645</v>
+        <v>24.84</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-0.38</v>
       </c>
       <c r="M6" t="n">
-        <v>0.4675</v>
+        <v>0.6525</v>
       </c>
       <c r="N6" t="n">
-        <v>18.82875</v>
+        <v>20.0275</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.17</v>
       </c>
       <c r="M7" t="n">
-        <v>0.4125</v>
+        <v>0.4825</v>
       </c>
       <c r="N7" t="n">
-        <v>17.5975</v>
+        <v>18.31</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.87</v>
       </c>
       <c r="M8" t="n">
-        <v>0.33</v>
+        <v>0.505</v>
       </c>
       <c r="N8" t="n">
-        <v>17.45125</v>
+        <v>18.3975</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1403,7 +1403,7 @@
         <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>3450</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>2977</v>
+      </c>
+      <c r="D75" t="n">
+        <v>2013</v>
+      </c>
+      <c r="E75" t="n">
+        <v>964</v>
+      </c>
+      <c r="F75" t="n">
+        <v>32.37</v>
+      </c>
+      <c r="G75" t="n">
+        <v>656</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>22.05%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>3</v>
+      </c>
+      <c r="J75" t="n">
+        <v>659</v>
+      </c>
+      <c r="K75" t="n">
+        <v>305</v>
+      </c>
+      <c r="L75" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="M75" t="n">
+        <v>1.35375</v>
+      </c>
+      <c r="N75" t="n">
+        <v>29.335</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X75" t="n">
+        <v>2.028985507246377</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>7.569999999999997</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.3052419354838709</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>2.943396226415094</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>1.559999999999999</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.05063291139240511</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
